--- a/Claude outputs/Mare_Durabilis_Budget_pluriannuel_FDD.xlsx
+++ b/Claude outputs/Mare_Durabilis_Budget_pluriannuel_FDD.xlsx
@@ -699,111 +699,111 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">Ressources!C27</f>
-        <v>1562972.03</v>
+        <v>1575594.53</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">Ressources!D27</f>
@@ -1133,11 +1133,11 @@
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">SUM(C7:E7)</f>
-        <v>3781272.03</v>
+        <v>3793894.53</v>
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">SUM(B7:E7)</f>
-        <v>3946065.98</v>
+        <v>3958688.48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">Ressources!C12+Ressources!C13+Ressources!C14</f>
-        <v>1562447.03</v>
+        <v>1575069.53</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">Ressources!D12+Ressources!D13+Ressources!D14</f>
@@ -1162,11 +1162,11 @@
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">SUM(C8:E8)</f>
-        <v>3778947.03</v>
+        <v>3791569.53</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">SUM(B8:E8)</f>
-        <v>3943665.98</v>
+        <v>3956288.48</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">C7</f>
-        <v>1562972.03</v>
+        <v>1575594.53</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">D7</f>
@@ -1220,11 +1220,11 @@
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">SUM(C10:E10)</f>
-        <v>3781272.03</v>
+        <v>3793894.53</v>
       </c>
       <c r="G10" s="14" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>3946065.98</v>
+        <v>3958688.48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1397,19 +1397,19 @@
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">'B · Moyens communs'!D10</f>
-        <v>27182.32</v>
+        <v>28740.58</v>
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">'B · Moyens communs'!E10</f>
-        <v>27884.82</v>
+        <v>38949.06</v>
       </c>
       <c r="F18" s="11" t="n">
         <f aca="false">SUM(C18:E18)</f>
-        <v>71310.49</v>
+        <v>83932.99</v>
       </c>
       <c r="G18" s="11" t="n">
         <f aca="false">SUM(B18:E18)</f>
-        <v>73430.49</v>
+        <v>86052.99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1455,19 +1455,19 @@
       </c>
       <c r="D20" s="16" t="n">
         <f aca="false">D17+D18+D19</f>
-        <v>2328767.12</v>
+        <v>2330325.38</v>
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">E17+E18+E19</f>
-        <v>351229.91</v>
+        <v>362294.15</v>
       </c>
       <c r="F20" s="17" t="n">
         <f aca="false">SUM(C20:E20)</f>
-        <v>3830645.98</v>
+        <v>3843268.48</v>
       </c>
       <c r="G20" s="17" t="n">
         <f aca="false">SUM(B20:E20)</f>
-        <v>3946065.98</v>
+        <v>3958688.48</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1491,19 +1491,19 @@
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">C10-C20</f>
-        <v>412323.08</v>
+        <v>424945.58</v>
       </c>
       <c r="D23" s="13" t="n">
         <f aca="false">D10-D20</f>
-        <v>-111367.12</v>
+        <v>-112925.38</v>
       </c>
       <c r="E23" s="13" t="n">
         <f aca="false">E10-E20</f>
-        <v>-350329.91</v>
+        <v>-361394.15</v>
       </c>
       <c r="F23" s="14" t="n">
         <f aca="false">SUM(C23:E23)</f>
-        <v>-49373.9499999998</v>
+        <v>-49373.9500000001</v>
       </c>
       <c r="G23" s="14" t="n">
         <f aca="false">SUM(B23:E23)</f>
@@ -1520,11 +1520,11 @@
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">B24+C23</f>
-        <v>461697.03</v>
+        <v>474319.53</v>
       </c>
       <c r="D24" s="14" t="n">
         <f aca="false">C24+D23</f>
-        <v>350329.91</v>
+        <v>361394.15</v>
       </c>
       <c r="E24" s="14" t="n">
         <f aca="false">D24+E23</f>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">Ressources!C13</f>
-        <v>1562447.03</v>
+        <v>1575069.53</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">Ressources!D13</f>
@@ -1874,11 +1874,11 @@
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">SUM(C10:E10)</f>
-        <v>1562447.03</v>
+        <v>1575069.53</v>
       </c>
       <c r="G10" s="11" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>1562447.03</v>
+        <v>1575069.53</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>44</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">SUM(C7:C23)</f>
-        <v>1592972.03</v>
+        <v>1605594.53</v>
       </c>
       <c r="D24" s="13" t="n">
         <f aca="false">SUM(D7:D23)</f>
@@ -2304,11 +2304,11 @@
       </c>
       <c r="F24" s="14" t="n">
         <f aca="false">SUM(C24:E24)</f>
-        <v>3811272.03</v>
+        <v>3823894.53</v>
       </c>
       <c r="G24" s="14" t="n">
         <f aca="false">SUM(B24:E24)</f>
-        <v>3991065.98</v>
+        <v>4003688.48</v>
       </c>
       <c r="H24" s="21"/>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="C25" s="13" t="n">
         <f aca="false">SUM(C8:C23)</f>
-        <v>1562972.03</v>
+        <v>1575594.53</v>
       </c>
       <c r="D25" s="13" t="n">
         <f aca="false">SUM(D8:D23)</f>
@@ -2334,11 +2334,11 @@
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">SUM(C25:E25)</f>
-        <v>3781272.03</v>
+        <v>3793894.53</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">SUM(B25:E25)</f>
-        <v>3946065.98</v>
+        <v>3958688.48</v>
       </c>
       <c r="H25" s="21"/>
     </row>
@@ -2532,19 +2532,19 @@
       </c>
       <c r="D35" s="10" t="n">
         <f aca="false">'B · Moyens communs'!D10</f>
-        <v>27182.32</v>
+        <v>28740.58</v>
       </c>
       <c r="E35" s="10" t="n">
         <f aca="false">'B · Moyens communs'!E10</f>
-        <v>27884.82</v>
+        <v>38949.06</v>
       </c>
       <c r="F35" s="11" t="n">
         <f aca="false">SUM(C35:E35)</f>
-        <v>71310.49</v>
+        <v>83932.99</v>
       </c>
       <c r="G35" s="11" t="n">
         <f aca="false">SUM(B35:E35)</f>
-        <v>73430.49</v>
+        <v>86052.99</v>
       </c>
       <c r="H35" s="21"/>
     </row>
@@ -2618,19 +2618,19 @@
       </c>
       <c r="D41" s="16" t="n">
         <f aca="false">D32+D35+D38</f>
-        <v>2328767.12</v>
+        <v>2330325.38</v>
       </c>
       <c r="E41" s="16" t="n">
         <f aca="false">E32+E35+E38</f>
-        <v>351229.91</v>
+        <v>362294.15</v>
       </c>
       <c r="F41" s="17" t="n">
         <f aca="false">SUM(C41:E41)</f>
-        <v>3830645.98</v>
+        <v>3843268.48</v>
       </c>
       <c r="G41" s="17" t="n">
         <f aca="false">SUM(B41:E41)</f>
-        <v>3946065.98</v>
+        <v>3958688.48</v>
       </c>
       <c r="H41" s="22"/>
     </row>
@@ -2644,19 +2644,19 @@
       </c>
       <c r="C42" s="13" t="n">
         <f aca="false">C25-C41</f>
-        <v>412323.08</v>
+        <v>424945.58</v>
       </c>
       <c r="D42" s="13" t="n">
         <f aca="false">D25-D41</f>
-        <v>-111367.12</v>
+        <v>-112925.38</v>
       </c>
       <c r="E42" s="13" t="n">
         <f aca="false">E25-E41</f>
-        <v>-350329.91</v>
+        <v>-361394.15</v>
       </c>
       <c r="F42" s="14" t="n">
         <f aca="false">SUM(C42:E42)</f>
-        <v>-49373.9499999998</v>
+        <v>-49373.9500000001</v>
       </c>
       <c r="G42" s="14" t="n">
         <f aca="false">SUM(B42:E42)</f>
@@ -2676,11 +2676,11 @@
       </c>
       <c r="C43" s="14" t="n">
         <f aca="false">B43+C42</f>
-        <v>461697.03</v>
+        <v>474319.53</v>
       </c>
       <c r="D43" s="14" t="n">
         <f aca="false">C43+D42</f>
-        <v>350329.91</v>
+        <v>361394.15</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">D43+E42</f>
@@ -5391,18 +5391,18 @@
         <v>15324.75</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>20546.52</v>
+        <v>22104.78</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>21002.73</v>
+        <v>32066.97</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">SUM(C9:E9)</f>
-        <v>56874</v>
+        <v>69496.5</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">SUM(B9:E9)</f>
-        <v>56874</v>
+        <v>69496.5</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>128</v>
@@ -5422,19 +5422,19 @@
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">SUM(D7:D9)</f>
-        <v>27182.32</v>
+        <v>28740.58</v>
       </c>
       <c r="E10" s="13" t="n">
         <f aca="false">SUM(E7:E9)</f>
-        <v>27884.82</v>
+        <v>38949.06</v>
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">SUM(C10:E10)</f>
-        <v>71310.49</v>
+        <v>83932.99</v>
       </c>
       <c r="G10" s="14" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>73430.49</v>
+        <v>86052.99</v>
       </c>
       <c r="H10" s="21"/>
     </row>
@@ -6014,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>1562447.03</v>
+        <v>1575069.53</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>0</v>
@@ -6024,11 +6024,11 @@
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">SUM(C13:E13)</f>
-        <v>1562447.03</v>
+        <v>1575069.53</v>
       </c>
       <c r="G13" s="11" t="n">
         <f aca="false">SUM(B13:E13)</f>
-        <v>1562447.03</v>
+        <v>1575069.53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="C27" s="16" t="n">
         <f aca="false">SUM(C11:C26)</f>
-        <v>1562972.03</v>
+        <v>1575594.53</v>
       </c>
       <c r="D27" s="16" t="n">
         <f aca="false">SUM(D11:D26)</f>
@@ -6378,11 +6378,11 @@
       </c>
       <c r="F27" s="17" t="n">
         <f aca="false">SUM(C27:E27)</f>
-        <v>3781272.03</v>
+        <v>3793894.53</v>
       </c>
       <c r="G27" s="17" t="n">
         <f aca="false">SUM(B27:E27)</f>
-        <v>3946065.98</v>
+        <v>3958688.48</v>
       </c>
     </row>
   </sheetData>

--- a/Claude outputs/Mare_Durabilis_Budget_pluriannuel_FDD.xlsx
+++ b/Claude outputs/Mare_Durabilis_Budget_pluriannuel_FDD.xlsx
@@ -1117,11 +1117,11 @@
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">Ressources!B27</f>
-        <v>164793.95</v>
+        <v>157527.72</v>
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">Ressources!C27</f>
-        <v>1575594.53</v>
+        <v>1568060.69</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">Ressources!D27</f>
@@ -1133,11 +1133,11 @@
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">SUM(C7:E7)</f>
-        <v>3793894.53</v>
+        <v>3786360.69</v>
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">SUM(B7:E7)</f>
-        <v>3958688.48</v>
+        <v>3943888.41</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="B8" s="10" t="n">
         <f aca="false">Ressources!B12+Ressources!B13+Ressources!B14</f>
-        <v>164718.95</v>
+        <v>157452.72</v>
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">Ressources!C12+Ressources!C13+Ressources!C14</f>
-        <v>1575069.53</v>
+        <v>1567535.69</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">Ressources!D12+Ressources!D13+Ressources!D14</f>
@@ -1162,11 +1162,11 @@
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">SUM(C8:E8)</f>
-        <v>3791569.53</v>
+        <v>3784035.69</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">SUM(B8:E8)</f>
-        <v>3956288.48</v>
+        <v>3941488.41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1204,11 +1204,11 @@
       </c>
       <c r="B10" s="13" t="n">
         <f aca="false">B7</f>
-        <v>164793.95</v>
+        <v>157527.72</v>
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">C7</f>
-        <v>1575594.53</v>
+        <v>1568060.69</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">D7</f>
@@ -1220,11 +1220,11 @@
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">SUM(C10:E10)</f>
-        <v>3793894.53</v>
+        <v>3786360.69</v>
       </c>
       <c r="G10" s="14" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>3958688.48</v>
+        <v>3943888.41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1393,23 +1393,23 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">'B · Moyens communs'!C10</f>
-        <v>16243.35</v>
+        <v>9707.23</v>
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">'B · Moyens communs'!D10</f>
-        <v>28740.58</v>
+        <v>25663.52</v>
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">'B · Moyens communs'!E10</f>
-        <v>38949.06</v>
+        <v>35216.28</v>
       </c>
       <c r="F18" s="11" t="n">
         <f aca="false">SUM(C18:E18)</f>
-        <v>83932.99</v>
+        <v>70587.03</v>
       </c>
       <c r="G18" s="11" t="n">
         <f aca="false">SUM(B18:E18)</f>
-        <v>86052.99</v>
+        <v>72707.03</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="C19" s="10" t="n">
         <f aca="false">'C · Fonctionnement'!C17</f>
-        <v>33055.6</v>
+        <v>32325.49</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">'C · Fonctionnement'!D17</f>
-        <v>60234.8</v>
+        <v>59875.72</v>
       </c>
       <c r="E19" s="10" t="n">
         <f aca="false">'C · Fonctionnement'!E17</f>
-        <v>62495.09</v>
+        <v>62130.17</v>
       </c>
       <c r="F19" s="11" t="n">
         <f aca="false">SUM(C19:E19)</f>
-        <v>155785.49</v>
+        <v>154331.38</v>
       </c>
       <c r="G19" s="11" t="n">
         <f aca="false">SUM(B19:E19)</f>
-        <v>156085.49</v>
+        <v>154631.38</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1451,23 +1451,23 @@
       </c>
       <c r="C20" s="16" t="n">
         <f aca="false">C17+C18+C19</f>
-        <v>1150648.95</v>
+        <v>1143382.72</v>
       </c>
       <c r="D20" s="16" t="n">
         <f aca="false">D17+D18+D19</f>
-        <v>2330325.38</v>
+        <v>2326889.24</v>
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">E17+E18+E19</f>
-        <v>362294.15</v>
+        <v>358196.45</v>
       </c>
       <c r="F20" s="17" t="n">
         <f aca="false">SUM(C20:E20)</f>
-        <v>3843268.48</v>
+        <v>3828468.41</v>
       </c>
       <c r="G20" s="17" t="n">
         <f aca="false">SUM(B20:E20)</f>
-        <v>3958688.48</v>
+        <v>3943888.41</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1487,23 +1487,23 @@
       </c>
       <c r="B23" s="13" t="n">
         <f aca="false">B10-B20</f>
-        <v>49373.95</v>
+        <v>42107.72</v>
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">C10-C20</f>
-        <v>424945.58</v>
+        <v>424677.97</v>
       </c>
       <c r="D23" s="13" t="n">
         <f aca="false">D10-D20</f>
-        <v>-112925.38</v>
+        <v>-109489.24</v>
       </c>
       <c r="E23" s="13" t="n">
         <f aca="false">E10-E20</f>
-        <v>-361394.15</v>
+        <v>-357296.45</v>
       </c>
       <c r="F23" s="14" t="n">
         <f aca="false">SUM(C23:E23)</f>
-        <v>-49373.9500000001</v>
+        <v>-42107.7200000003</v>
       </c>
       <c r="G23" s="14" t="n">
         <f aca="false">SUM(B23:E23)</f>
@@ -1516,15 +1516,15 @@
       </c>
       <c r="B24" s="14" t="n">
         <f aca="false">B23</f>
-        <v>49373.95</v>
+        <v>42107.72</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">B24+C23</f>
-        <v>474319.53</v>
+        <v>466785.69</v>
       </c>
       <c r="D24" s="14" t="n">
         <f aca="false">C24+D23</f>
-        <v>361394.15</v>
+        <v>357296.45</v>
       </c>
       <c r="E24" s="14" t="n">
         <f aca="false">D24+E23</f>
@@ -1611,21 +1611,21 @@
         <v>0</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>32545.98</v>
+        <v>29607.11</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>58905.23</v>
+        <v>55110.94</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>59571.57</v>
+        <v>55804.3</v>
       </c>
       <c r="F31" s="11" t="n">
         <f aca="false">SUM(C31:E31)</f>
-        <v>151022.78</v>
+        <v>140522.35</v>
       </c>
       <c r="G31" s="11" t="n">
         <f aca="false">SUM(B31:E31)</f>
-        <v>151022.78</v>
+        <v>140522.35</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1636,21 +1636,21 @@
         <v>0</v>
       </c>
       <c r="C32" s="19" t="n">
-        <v>14011.2</v>
+        <v>12550.98</v>
       </c>
       <c r="D32" s="19" t="n">
-        <v>26245.6</v>
+        <v>25527.44</v>
       </c>
       <c r="E32" s="19" t="n">
-        <v>26738.18</v>
+        <v>26008.34</v>
       </c>
       <c r="F32" s="11" t="n">
         <f aca="false">SUM(C32:E32)</f>
-        <v>66994.98</v>
+        <v>64086.76</v>
       </c>
       <c r="G32" s="11" t="n">
         <f aca="false">SUM(B32:E32)</f>
-        <v>66994.98</v>
+        <v>64086.76</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">Ressources!B12</f>
-        <v>164718.95</v>
+        <v>157452.72</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">Ressources!C12</f>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">SUM(B9:E9)</f>
-        <v>164718.95</v>
+        <v>157452.72</v>
       </c>
       <c r="H9" s="21" t="s">
         <v>42</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">Ressources!C13</f>
-        <v>1575069.53</v>
+        <v>1567535.69</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">Ressources!D13</f>
@@ -1874,11 +1874,11 @@
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">SUM(C10:E10)</f>
-        <v>1575069.53</v>
+        <v>1567535.69</v>
       </c>
       <c r="G10" s="11" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>1575069.53</v>
+        <v>1567535.69</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>44</v>
@@ -2288,11 +2288,11 @@
       </c>
       <c r="B24" s="13" t="n">
         <f aca="false">SUM(B7:B23)</f>
-        <v>179793.95</v>
+        <v>172527.72</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">SUM(C7:C23)</f>
-        <v>1605594.53</v>
+        <v>1598060.69</v>
       </c>
       <c r="D24" s="13" t="n">
         <f aca="false">SUM(D7:D23)</f>
@@ -2304,11 +2304,11 @@
       </c>
       <c r="F24" s="14" t="n">
         <f aca="false">SUM(C24:E24)</f>
-        <v>3823894.53</v>
+        <v>3816360.69</v>
       </c>
       <c r="G24" s="14" t="n">
         <f aca="false">SUM(B24:E24)</f>
-        <v>4003688.48</v>
+        <v>3988888.41</v>
       </c>
       <c r="H24" s="21"/>
     </row>
@@ -2318,11 +2318,11 @@
       </c>
       <c r="B25" s="13" t="n">
         <f aca="false">SUM(B8:B23)</f>
-        <v>164793.95</v>
+        <v>157527.72</v>
       </c>
       <c r="C25" s="13" t="n">
         <f aca="false">SUM(C8:C23)</f>
-        <v>1575594.53</v>
+        <v>1568060.69</v>
       </c>
       <c r="D25" s="13" t="n">
         <f aca="false">SUM(D8:D23)</f>
@@ -2334,11 +2334,11 @@
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">SUM(C25:E25)</f>
-        <v>3793894.53</v>
+        <v>3786360.69</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">SUM(B25:E25)</f>
-        <v>3958688.48</v>
+        <v>3943888.41</v>
       </c>
       <c r="H25" s="21"/>
     </row>
@@ -2528,23 +2528,23 @@
       </c>
       <c r="C35" s="10" t="n">
         <f aca="false">'B · Moyens communs'!C10</f>
-        <v>16243.35</v>
+        <v>9707.23</v>
       </c>
       <c r="D35" s="10" t="n">
         <f aca="false">'B · Moyens communs'!D10</f>
-        <v>28740.58</v>
+        <v>25663.52</v>
       </c>
       <c r="E35" s="10" t="n">
         <f aca="false">'B · Moyens communs'!E10</f>
-        <v>38949.06</v>
+        <v>35216.28</v>
       </c>
       <c r="F35" s="11" t="n">
         <f aca="false">SUM(C35:E35)</f>
-        <v>83932.99</v>
+        <v>70587.03</v>
       </c>
       <c r="G35" s="11" t="n">
         <f aca="false">SUM(B35:E35)</f>
-        <v>86052.99</v>
+        <v>72707.03</v>
       </c>
       <c r="H35" s="21"/>
     </row>
@@ -2571,23 +2571,23 @@
       </c>
       <c r="C38" s="10" t="n">
         <f aca="false">'C · Fonctionnement'!C17</f>
-        <v>33055.6</v>
+        <v>32325.49</v>
       </c>
       <c r="D38" s="10" t="n">
         <f aca="false">'C · Fonctionnement'!D17</f>
-        <v>60234.8</v>
+        <v>59875.72</v>
       </c>
       <c r="E38" s="10" t="n">
         <f aca="false">'C · Fonctionnement'!E17</f>
-        <v>62495.09</v>
+        <v>62130.17</v>
       </c>
       <c r="F38" s="11" t="n">
         <f aca="false">SUM(C38:E38)</f>
-        <v>155785.49</v>
+        <v>154331.38</v>
       </c>
       <c r="G38" s="11" t="n">
         <f aca="false">SUM(B38:E38)</f>
-        <v>156085.49</v>
+        <v>154631.38</v>
       </c>
       <c r="H38" s="21"/>
     </row>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="C41" s="16" t="n">
         <f aca="false">C32+C35+C38</f>
-        <v>1150648.95</v>
+        <v>1143382.72</v>
       </c>
       <c r="D41" s="16" t="n">
         <f aca="false">D32+D35+D38</f>
-        <v>2330325.38</v>
+        <v>2326889.24</v>
       </c>
       <c r="E41" s="16" t="n">
         <f aca="false">E32+E35+E38</f>
-        <v>362294.15</v>
+        <v>358196.45</v>
       </c>
       <c r="F41" s="17" t="n">
         <f aca="false">SUM(C41:E41)</f>
-        <v>3843268.48</v>
+        <v>3828468.41</v>
       </c>
       <c r="G41" s="17" t="n">
         <f aca="false">SUM(B41:E41)</f>
-        <v>3958688.48</v>
+        <v>3943888.41</v>
       </c>
       <c r="H41" s="22"/>
     </row>
@@ -2640,23 +2640,23 @@
       </c>
       <c r="B42" s="13" t="n">
         <f aca="false">B25-B41</f>
-        <v>49373.95</v>
+        <v>42107.72</v>
       </c>
       <c r="C42" s="13" t="n">
         <f aca="false">C25-C41</f>
-        <v>424945.58</v>
+        <v>424677.97</v>
       </c>
       <c r="D42" s="13" t="n">
         <f aca="false">D25-D41</f>
-        <v>-112925.38</v>
+        <v>-109489.24</v>
       </c>
       <c r="E42" s="13" t="n">
         <f aca="false">E25-E41</f>
-        <v>-361394.15</v>
+        <v>-357296.45</v>
       </c>
       <c r="F42" s="14" t="n">
         <f aca="false">SUM(C42:E42)</f>
-        <v>-49373.9500000001</v>
+        <v>-42107.7200000003</v>
       </c>
       <c r="G42" s="14" t="n">
         <f aca="false">SUM(B42:E42)</f>
@@ -2672,15 +2672,15 @@
       </c>
       <c r="B43" s="14" t="n">
         <f aca="false">B42</f>
-        <v>49373.95</v>
+        <v>42107.72</v>
       </c>
       <c r="C43" s="14" t="n">
         <f aca="false">B43+C42</f>
-        <v>474319.53</v>
+        <v>466785.69</v>
       </c>
       <c r="D43" s="14" t="n">
         <f aca="false">C43+D42</f>
-        <v>361394.15</v>
+        <v>357296.45</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">D43+E42</f>
@@ -2710,23 +2710,23 @@
       </c>
       <c r="C46" s="10" t="n">
         <f aca="false">Synthèse!C31</f>
-        <v>32545.98</v>
+        <v>29607.11</v>
       </c>
       <c r="D46" s="10" t="n">
         <f aca="false">Synthèse!D31</f>
-        <v>58905.23</v>
+        <v>55110.94</v>
       </c>
       <c r="E46" s="10" t="n">
         <f aca="false">Synthèse!E31</f>
-        <v>59571.57</v>
+        <v>55804.3</v>
       </c>
       <c r="F46" s="11" t="n">
         <f aca="false">SUM(C46:E46)</f>
-        <v>151022.78</v>
+        <v>140522.35</v>
       </c>
       <c r="G46" s="11" t="n">
         <f aca="false">SUM(B46:E46)</f>
-        <v>151022.78</v>
+        <v>140522.35</v>
       </c>
       <c r="H46" s="21"/>
     </row>
@@ -5332,21 +5332,21 @@
         <v>0</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>918.6</v>
+        <v>188.49</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>6635.8</v>
+        <v>6276.72</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>6882.09</v>
+        <v>6517.17</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">SUM(C7:E7)</f>
-        <v>14436.49</v>
+        <v>12982.38</v>
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">SUM(B7:E7)</f>
-        <v>14436.49</v>
+        <v>12982.38</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>124</v>
@@ -5388,21 +5388,21 @@
         <v>0</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>15324.75</v>
+        <v>9518.74</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>22104.78</v>
+        <v>19386.8</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>32066.97</v>
+        <v>28699.11</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">SUM(C9:E9)</f>
-        <v>69496.5</v>
+        <v>57604.65</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">SUM(B9:E9)</f>
-        <v>69496.5</v>
+        <v>57604.65</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>128</v>
@@ -5418,23 +5418,23 @@
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">SUM(C7:C9)</f>
-        <v>16243.35</v>
+        <v>9707.23</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">SUM(D7:D9)</f>
-        <v>28740.58</v>
+        <v>25663.52</v>
       </c>
       <c r="E10" s="13" t="n">
         <f aca="false">SUM(E7:E9)</f>
-        <v>38949.06</v>
+        <v>35216.28</v>
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">SUM(C10:E10)</f>
-        <v>83932.99</v>
+        <v>70587.03</v>
       </c>
       <c r="G10" s="14" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>86052.99</v>
+        <v>72707.03</v>
       </c>
       <c r="H10" s="21"/>
     </row>
@@ -5524,21 +5524,21 @@
         <v>0</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>5766</v>
+        <v>5685.66</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>11756.4</v>
+        <v>11598.75</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>11985.29</v>
+        <v>11830.72</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">SUM(C7:E7)</f>
-        <v>29507.69</v>
+        <v>29115.13</v>
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">SUM(B7:E7)</f>
-        <v>29507.69</v>
+        <v>29115.13</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>134</v>
@@ -5686,21 +5686,21 @@
         <v>0</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>1239.6</v>
+        <v>589.83</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>1366.4</v>
+        <v>1164.97</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>1383.8</v>
+        <v>1173.45</v>
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">SUM(C13:E13)</f>
-        <v>3989.8</v>
+        <v>2928.25</v>
       </c>
       <c r="G13" s="11" t="n">
         <f aca="false">SUM(B13:E13)</f>
-        <v>3989.8</v>
+        <v>2928.25</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>143</v>
@@ -5800,23 +5800,23 @@
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">SUM(C7:C16)</f>
-        <v>33055.6</v>
+        <v>32325.49</v>
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">SUM(D7:D16)</f>
-        <v>60234.8</v>
+        <v>59875.72</v>
       </c>
       <c r="E17" s="13" t="n">
         <f aca="false">SUM(E7:E16)</f>
-        <v>62495.09</v>
+        <v>62130.17</v>
       </c>
       <c r="F17" s="14" t="n">
         <f aca="false">SUM(C17:E17)</f>
-        <v>155785.49</v>
+        <v>154331.38</v>
       </c>
       <c r="G17" s="14" t="n">
         <f aca="false">SUM(B17:E17)</f>
-        <v>156085.49</v>
+        <v>154631.38</v>
       </c>
       <c r="H17" s="21"/>
     </row>
@@ -5986,7 +5986,7 @@
         <v>158</v>
       </c>
       <c r="B12" s="19" t="n">
-        <v>164718.95</v>
+        <v>157452.72</v>
       </c>
       <c r="C12" s="19" t="n">
         <v>0</v>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="G12" s="11" t="n">
         <f aca="false">SUM(B12:E12)</f>
-        <v>164718.95</v>
+        <v>157452.72</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6014,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>1575069.53</v>
+        <v>1567535.69</v>
       </c>
       <c r="D13" s="19" t="n">
         <v>0</v>
@@ -6024,11 +6024,11 @@
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">SUM(C13:E13)</f>
-        <v>1575069.53</v>
+        <v>1567535.69</v>
       </c>
       <c r="G13" s="11" t="n">
         <f aca="false">SUM(B13:E13)</f>
-        <v>1575069.53</v>
+        <v>1567535.69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6362,11 +6362,11 @@
       </c>
       <c r="B27" s="16" t="n">
         <f aca="false">SUM(B11:B26)</f>
-        <v>164793.95</v>
+        <v>157527.72</v>
       </c>
       <c r="C27" s="16" t="n">
         <f aca="false">SUM(C11:C26)</f>
-        <v>1575594.53</v>
+        <v>1568060.69</v>
       </c>
       <c r="D27" s="16" t="n">
         <f aca="false">SUM(D11:D26)</f>
@@ -6378,11 +6378,11 @@
       </c>
       <c r="F27" s="17" t="n">
         <f aca="false">SUM(C27:E27)</f>
-        <v>3793894.53</v>
+        <v>3786360.69</v>
       </c>
       <c r="G27" s="17" t="n">
         <f aca="false">SUM(B27:E27)</f>
-        <v>3958688.48</v>
+        <v>3943888.41</v>
       </c>
     </row>
   </sheetData>
